--- a/05 Others/2026.1 Avaliação Projetos/Turma Gestão de Informação - WYD6917 Turma 1001 PRESENCIAL Wyden UniRuy 2026_1.xlsx
+++ b/05 Others/2026.1 Avaliação Projetos/Turma Gestão de Informação - WYD6917 Turma 1001 PRESENCIAL Wyden UniRuy 2026_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YduqsArea1\Avaliações Yduqs 2022_2 BDQ 2023_1 2024_2\2026.1 Avaliação Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16FAC6C-0D35-465E-940F-70AEFC5204FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6103B0A6-ADE4-4233-B2DF-CE882FDA582B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DD6ED3E7-57DF-4A52-9E4C-63B0F7661B3D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>ALUNO</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>não GitHub</t>
+  </si>
+  <si>
+    <t>atrasos; não SAVA atv 2 e atv 4</t>
   </si>
 </sst>
 </file>
@@ -87,7 +90,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,6 +144,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -358,7 +367,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -408,6 +417,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -784,19 +796,19 @@
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="16">
         <f>B3</f>
-        <v>9</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>14</v>
       </c>
       <c r="E3" s="1"/>
     </row>
